--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3681,6 +3681,121 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>114700664</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97528</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ekdalsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>628040</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6645559</v>
+      </c>
+      <c r="S28" t="n">
+        <v>14</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C-Upp-0700</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-10-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-10-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -4273,7 +4273,7 @@
         <v>115495579</v>
       </c>
       <c r="B33" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>116372637</v>
       </c>
       <c r="B45" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6294,10 +6294,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121063691</v>
+        <v>121063659</v>
       </c>
       <c r="B50" t="n">
-        <v>98071</v>
+        <v>91312</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6306,52 +6306,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628131</v>
+        <v>628118</v>
       </c>
       <c r="R50" t="n">
-        <v>6645738</v>
+        <v>6645721</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6383,7 +6369,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6393,7 +6379,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6420,10 +6406,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121075787</v>
+        <v>121064118</v>
       </c>
       <c r="B51" t="n">
-        <v>79679</v>
+        <v>94604</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6432,44 +6418,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2818</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ekdalsröret, Upl</t>
+          <t>Uppsala, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628029</v>
+        <v>628010</v>
       </c>
       <c r="R51" t="n">
-        <v>6645577</v>
+        <v>6645722</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6498,7 +6481,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6508,12 +6491,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6522,29 +6500,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121063659</v>
+        <v>121064006</v>
       </c>
       <c r="B52" t="n">
-        <v>91302</v>
+        <v>97037</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6557,34 +6534,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1339</v>
+        <v>224363</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Uppsala, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628118</v>
+        <v>627998</v>
       </c>
       <c r="R52" t="n">
-        <v>6645721</v>
+        <v>6645748</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6616,7 +6589,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6626,7 +6599,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6653,10 +6626,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121064006</v>
+        <v>121063293</v>
       </c>
       <c r="B53" t="n">
-        <v>97027</v>
+        <v>100347</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6669,30 +6642,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>224363</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Uppsala, Uppsala, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>627998</v>
+        <v>628176</v>
       </c>
       <c r="R53" t="n">
-        <v>6645748</v>
+        <v>6645798</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6724,7 +6701,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6734,7 +6711,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6764,7 +6741,7 @@
         <v>121063804</v>
       </c>
       <c r="B54" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6878,10 +6855,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121075770</v>
+        <v>121075787</v>
       </c>
       <c r="B55" t="n">
-        <v>97025</v>
+        <v>79682</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6890,31 +6867,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6922,10 +6898,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>627994</v>
+        <v>628029</v>
       </c>
       <c r="R55" t="n">
-        <v>6645755</v>
+        <v>6645577</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6957,7 +6933,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6967,7 +6943,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6995,10 +6976,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121062863</v>
+        <v>121063691</v>
       </c>
       <c r="B56" t="n">
-        <v>105176</v>
+        <v>98081</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7007,25 +6988,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -7035,7 +7016,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -7049,10 +7030,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628253</v>
+        <v>628131</v>
       </c>
       <c r="R56" t="n">
-        <v>6645900</v>
+        <v>6645738</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7084,7 +7065,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7094,12 +7075,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>I avverkningsanmäld skog</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7126,10 +7102,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121064118</v>
+        <v>121063186</v>
       </c>
       <c r="B57" t="n">
-        <v>94594</v>
+        <v>98081</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7138,38 +7114,52 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Uppsala, Uppsala, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628010</v>
+        <v>628227</v>
       </c>
       <c r="R57" t="n">
-        <v>6645722</v>
+        <v>6645791</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7201,7 +7191,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7211,7 +7201,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>I avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7241,7 +7236,7 @@
         <v>121063571</v>
       </c>
       <c r="B58" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7364,10 +7359,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121063186</v>
+        <v>121062863</v>
       </c>
       <c r="B59" t="n">
-        <v>98071</v>
+        <v>105186</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7376,40 +7371,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7418,10 +7413,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628227</v>
+        <v>628253</v>
       </c>
       <c r="R59" t="n">
-        <v>6645791</v>
+        <v>6645900</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7453,7 +7448,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7463,7 +7458,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7495,10 +7490,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121063293</v>
+        <v>121075770</v>
       </c>
       <c r="B60" t="n">
-        <v>100337</v>
+        <v>97035</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7511,37 +7506,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628176</v>
+        <v>627994</v>
       </c>
       <c r="R60" t="n">
-        <v>6645798</v>
+        <v>6645755</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7570,7 +7569,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7580,7 +7579,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7589,18 +7588,19 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -6518,10 +6518,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121064006</v>
+        <v>121063293</v>
       </c>
       <c r="B52" t="n">
-        <v>97037</v>
+        <v>100347</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6534,30 +6534,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>224363</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Uppsala, Uppsala, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>627998</v>
+        <v>628176</v>
       </c>
       <c r="R52" t="n">
-        <v>6645748</v>
+        <v>6645798</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6589,7 +6593,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6599,7 +6603,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6626,10 +6630,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121063293</v>
+        <v>121064006</v>
       </c>
       <c r="B53" t="n">
-        <v>100347</v>
+        <v>97037</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6642,34 +6646,30 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>224363</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Uppsala, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>628176</v>
+        <v>627998</v>
       </c>
       <c r="R53" t="n">
-        <v>6645798</v>
+        <v>6645748</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -6518,10 +6518,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121063293</v>
+        <v>121064006</v>
       </c>
       <c r="B52" t="n">
-        <v>100347</v>
+        <v>97037</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6534,34 +6534,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>224363</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Uppsala, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628176</v>
+        <v>627998</v>
       </c>
       <c r="R52" t="n">
-        <v>6645798</v>
+        <v>6645748</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6593,7 +6589,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6603,7 +6599,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6630,10 +6626,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121064006</v>
+        <v>121063293</v>
       </c>
       <c r="B53" t="n">
-        <v>97037</v>
+        <v>100347</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6646,30 +6642,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>224363</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Uppsala, Uppsala, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>627998</v>
+        <v>628176</v>
       </c>
       <c r="R53" t="n">
-        <v>6645748</v>
+        <v>6645798</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -6294,10 +6294,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121063659</v>
+        <v>121063691</v>
       </c>
       <c r="B50" t="n">
-        <v>91312</v>
+        <v>98081</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6306,38 +6306,52 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628118</v>
+        <v>628131</v>
       </c>
       <c r="R50" t="n">
-        <v>6645721</v>
+        <v>6645738</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6369,7 +6383,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6379,7 +6393,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6406,10 +6420,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121064118</v>
+        <v>121063804</v>
       </c>
       <c r="B51" t="n">
-        <v>94604</v>
+        <v>90715</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6418,38 +6432,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2818</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Uppsala, Uppsala, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628010</v>
+        <v>628125</v>
       </c>
       <c r="R51" t="n">
-        <v>6645722</v>
+        <v>6645764</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6481,7 +6495,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6491,7 +6505,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre och någon mindre yngre fruktkropp på vindfälle.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6518,10 +6537,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121064006</v>
+        <v>121063571</v>
       </c>
       <c r="B52" t="n">
-        <v>97037</v>
+        <v>57504</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6530,34 +6549,52 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>224363</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Uppsala, Uppsala, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>627998</v>
+        <v>628155</v>
       </c>
       <c r="R52" t="n">
-        <v>6645748</v>
+        <v>6645804</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6589,7 +6626,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6599,7 +6636,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6626,10 +6663,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121063293</v>
+        <v>121064006</v>
       </c>
       <c r="B53" t="n">
-        <v>100347</v>
+        <v>97037</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6642,34 +6679,30 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>224363</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Uppsala, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>628176</v>
+        <v>627998</v>
       </c>
       <c r="R53" t="n">
-        <v>6645798</v>
+        <v>6645748</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6701,7 +6734,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6711,7 +6744,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6738,10 +6771,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121063804</v>
+        <v>121075787</v>
       </c>
       <c r="B54" t="n">
-        <v>90715</v>
+        <v>79682</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6754,37 +6787,40 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>628125</v>
+        <v>628029</v>
       </c>
       <c r="R54" t="n">
-        <v>6645764</v>
+        <v>6645577</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6813,7 +6849,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6823,12 +6859,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre och någon mindre yngre fruktkropp på vindfälle.</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6837,28 +6873,29 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121075787</v>
+        <v>121063186</v>
       </c>
       <c r="B55" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6867,44 +6904,55 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ekdalsröret, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>628029</v>
+        <v>628227</v>
       </c>
       <c r="R55" t="n">
-        <v>6645577</v>
+        <v>6645791</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6933,7 +6981,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6943,12 +6991,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>I avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6957,29 +7005,28 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121063691</v>
+        <v>121075770</v>
       </c>
       <c r="B56" t="n">
-        <v>98081</v>
+        <v>97035</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6988,55 +7035,45 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628131</v>
+        <v>627994</v>
       </c>
       <c r="R56" t="n">
-        <v>6645738</v>
+        <v>6645755</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7065,7 +7102,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7075,7 +7112,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7084,28 +7121,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121063186</v>
+        <v>121062863</v>
       </c>
       <c r="B57" t="n">
-        <v>98081</v>
+        <v>105186</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7114,40 +7152,40 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7156,10 +7194,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628227</v>
+        <v>628253</v>
       </c>
       <c r="R57" t="n">
-        <v>6645791</v>
+        <v>6645900</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7191,7 +7229,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7201,7 +7239,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7233,10 +7271,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121063571</v>
+        <v>121063659</v>
       </c>
       <c r="B58" t="n">
-        <v>57504</v>
+        <v>91312</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7245,52 +7283,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>628155</v>
+        <v>628118</v>
       </c>
       <c r="R58" t="n">
-        <v>6645804</v>
+        <v>6645721</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7322,7 +7346,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7332,7 +7356,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7359,10 +7383,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121062863</v>
+        <v>121064118</v>
       </c>
       <c r="B59" t="n">
-        <v>105186</v>
+        <v>94604</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7375,48 +7399,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>2818</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Uppsala, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628253</v>
+        <v>628010</v>
       </c>
       <c r="R59" t="n">
-        <v>6645900</v>
+        <v>6645722</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7448,7 +7458,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7458,12 +7468,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>I avverkningsanmäld skog</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7490,10 +7495,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121075770</v>
+        <v>121063293</v>
       </c>
       <c r="B60" t="n">
-        <v>97035</v>
+        <v>100347</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7506,41 +7511,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ekdalsröret, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>627994</v>
+        <v>628176</v>
       </c>
       <c r="R60" t="n">
-        <v>6645755</v>
+        <v>6645798</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7569,7 +7570,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7579,7 +7580,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7588,19 +7589,18 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -6294,10 +6294,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121063691</v>
+        <v>121063804</v>
       </c>
       <c r="B50" t="n">
-        <v>98081</v>
+        <v>90727</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6306,52 +6306,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628131</v>
+        <v>628125</v>
       </c>
       <c r="R50" t="n">
-        <v>6645738</v>
+        <v>6645764</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6383,7 +6369,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6393,7 +6379,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre och någon mindre yngre fruktkropp på vindfälle.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6420,10 +6411,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121063804</v>
+        <v>121063293</v>
       </c>
       <c r="B51" t="n">
-        <v>90715</v>
+        <v>100360</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6432,25 +6423,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6460,10 +6451,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628125</v>
+        <v>628176</v>
       </c>
       <c r="R51" t="n">
-        <v>6645764</v>
+        <v>6645798</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6495,7 +6486,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6505,12 +6496,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre och någon mindre yngre fruktkropp på vindfälle.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6537,10 +6523,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121063571</v>
+        <v>121063691</v>
       </c>
       <c r="B52" t="n">
-        <v>57504</v>
+        <v>98094</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6549,40 +6535,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6591,10 +6577,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628155</v>
+        <v>628131</v>
       </c>
       <c r="R52" t="n">
-        <v>6645804</v>
+        <v>6645738</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6626,7 +6612,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6636,7 +6622,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6663,10 +6649,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121064006</v>
+        <v>121062863</v>
       </c>
       <c r="B53" t="n">
-        <v>97037</v>
+        <v>105199</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6679,30 +6665,48 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>224363</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Uppsala, Uppsala, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>627998</v>
+        <v>628253</v>
       </c>
       <c r="R53" t="n">
-        <v>6645748</v>
+        <v>6645900</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6734,7 +6738,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6744,7 +6748,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>I avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6771,10 +6780,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121075787</v>
+        <v>121075770</v>
       </c>
       <c r="B54" t="n">
-        <v>79682</v>
+        <v>97048</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6783,30 +6792,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6814,10 +6824,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>628029</v>
+        <v>627994</v>
       </c>
       <c r="R54" t="n">
-        <v>6645577</v>
+        <v>6645755</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6849,7 +6859,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6859,12 +6869,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6892,10 +6897,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121063186</v>
+        <v>121063659</v>
       </c>
       <c r="B55" t="n">
-        <v>98081</v>
+        <v>91324</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6904,52 +6909,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>628227</v>
+        <v>628118</v>
       </c>
       <c r="R55" t="n">
-        <v>6645791</v>
+        <v>6645721</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6981,7 +6972,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6991,12 +6982,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>I avverkningsanmäld skog</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7023,10 +7009,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121075770</v>
+        <v>121075787</v>
       </c>
       <c r="B56" t="n">
-        <v>97035</v>
+        <v>79685</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7035,31 +7021,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7067,10 +7052,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>627994</v>
+        <v>628029</v>
       </c>
       <c r="R56" t="n">
-        <v>6645755</v>
+        <v>6645577</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -7102,7 +7087,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7112,7 +7097,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7140,10 +7130,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121062863</v>
+        <v>121064006</v>
       </c>
       <c r="B57" t="n">
-        <v>105186</v>
+        <v>97050</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7156,48 +7146,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>224363</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Uppsala, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628253</v>
+        <v>627998</v>
       </c>
       <c r="R57" t="n">
-        <v>6645900</v>
+        <v>6645748</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7229,7 +7201,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7239,12 +7211,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>I avverkningsanmäld skog</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7271,10 +7238,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121063659</v>
+        <v>121064118</v>
       </c>
       <c r="B58" t="n">
-        <v>91312</v>
+        <v>94616</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7287,34 +7254,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Uppsala, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>628118</v>
+        <v>628010</v>
       </c>
       <c r="R58" t="n">
-        <v>6645721</v>
+        <v>6645722</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7346,7 +7313,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7356,7 +7323,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7383,10 +7350,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121064118</v>
+        <v>121063571</v>
       </c>
       <c r="B59" t="n">
-        <v>94604</v>
+        <v>57504</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7395,38 +7362,52 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2818</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Uppsala, Uppsala, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628010</v>
+        <v>628155</v>
       </c>
       <c r="R59" t="n">
-        <v>6645722</v>
+        <v>6645804</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7458,7 +7439,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7468,7 +7449,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7495,10 +7476,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121063293</v>
+        <v>121063186</v>
       </c>
       <c r="B60" t="n">
-        <v>100347</v>
+        <v>98094</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7507,38 +7488,52 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628176</v>
+        <v>628227</v>
       </c>
       <c r="R60" t="n">
-        <v>6645798</v>
+        <v>6645791</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7570,7 +7565,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7580,7 +7575,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>I avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -4273,7 +4273,7 @@
         <v>115495579</v>
       </c>
       <c r="B33" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>116372637</v>
       </c>
       <c r="B45" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -4273,7 +4273,7 @@
         <v>115495579</v>
       </c>
       <c r="B33" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>116372637</v>
       </c>
       <c r="B45" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -4273,7 +4273,7 @@
         <v>115495579</v>
       </c>
       <c r="B33" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>116372637</v>
       </c>
       <c r="B45" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -4273,7 +4273,7 @@
         <v>115495579</v>
       </c>
       <c r="B33" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>116372637</v>
       </c>
       <c r="B45" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -5835,11 +5835,11 @@
         <v>116372591</v>
       </c>
       <c r="B46" t="n">
-        <v>57426</v>
+        <v>57631</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -7353,11 +7353,11 @@
         <v>121063571</v>
       </c>
       <c r="B59" t="n">
-        <v>57504</v>
+        <v>57631</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -5835,7 +5835,7 @@
         <v>116372591</v>
       </c>
       <c r="B46" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>121063571</v>
       </c>
       <c r="B59" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3683,10 +3683,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>114700664</v>
+        <v>115492128</v>
       </c>
       <c r="B28" t="n">
-        <v>97650</v>
+        <v>96610</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3695,45 +3695,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ekdalsröret, Upl</t>
+          <t>Ekdalsröret (Ekdalsröret), Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628040</v>
+        <v>628155</v>
       </c>
       <c r="R28" t="n">
-        <v>6645559</v>
+        <v>6645785</v>
       </c>
       <c r="S28" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3755,19 +3751,29 @@
           <t>Jumkil</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>C-Upp-0700</t>
-        </is>
-      </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3782,26 +3788,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115492128</v>
+        <v>115493598</v>
       </c>
       <c r="B29" t="n">
-        <v>96610</v>
+        <v>97650</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3810,38 +3812,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ekdalsröret (Ekdalsröret), Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628155</v>
+        <v>628224</v>
       </c>
       <c r="R29" t="n">
-        <v>6645785</v>
+        <v>6645790</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3873,7 +3889,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,12 +3899,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3915,10 +3926,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115493598</v>
+        <v>115492138</v>
       </c>
       <c r="B30" t="n">
-        <v>97650</v>
+        <v>91023</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3927,55 +3938,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ekdalsröret (Ekdalsröret), Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628224</v>
+        <v>628157</v>
       </c>
       <c r="R30" t="n">
-        <v>6645790</v>
+        <v>6645780</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4004,7 +4001,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4014,7 +4011,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4029,22 +4026,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115492138</v>
+        <v>115495242</v>
       </c>
       <c r="B31" t="n">
-        <v>91023</v>
+        <v>56478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4057,34 +4054,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ekdalsröret (Ekdalsröret), Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628157</v>
+        <v>628490</v>
       </c>
       <c r="R31" t="n">
-        <v>6645780</v>
+        <v>6645645</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4116,7 +4118,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4126,7 +4128,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4153,58 +4155,58 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115495242</v>
+        <v>115495579</v>
       </c>
       <c r="B32" t="n">
-        <v>56478</v>
+        <v>57357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Renfansberget, Renfansberget, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628490</v>
+        <v>628430</v>
       </c>
       <c r="R32" t="n">
-        <v>6645645</v>
+        <v>6645685</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4233,7 +4235,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4243,7 +4245,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Barkflagor borthackade i schackmönster bedömda som trolig tretåig hackspett av Annika Rastén.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4258,67 +4265,62 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115495579</v>
+        <v>115491409</v>
       </c>
       <c r="B33" t="n">
-        <v>57357</v>
+        <v>104737</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Renfansberget, Renfansberget, Upl</t>
+          <t>Ekdalsröret (Ekdalsröret), Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628430</v>
+        <v>628141</v>
       </c>
       <c r="R33" t="n">
-        <v>6645685</v>
+        <v>6645698</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4350,7 +4352,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4360,12 +4362,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Barkflagor borthackade i schackmönster bedömda som trolig tretåig hackspett av Annika Rastén.</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4380,22 +4377,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115491409</v>
+        <v>115492559</v>
       </c>
       <c r="B34" t="n">
-        <v>104737</v>
+        <v>96610</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4408,21 +4405,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4432,10 +4429,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628141</v>
+        <v>628205</v>
       </c>
       <c r="R34" t="n">
-        <v>6645698</v>
+        <v>6645803</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4467,7 +4464,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4477,7 +4474,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4492,22 +4489,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115492559</v>
+        <v>115495315</v>
       </c>
       <c r="B35" t="n">
-        <v>96610</v>
+        <v>79099</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4516,25 +4513,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4544,13 +4541,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628205</v>
+        <v>628497</v>
       </c>
       <c r="R35" t="n">
-        <v>6645803</v>
+        <v>6645645</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4579,7 +4576,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4589,7 +4586,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4604,22 +4601,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115495315</v>
+        <v>115495166</v>
       </c>
       <c r="B36" t="n">
-        <v>79099</v>
+        <v>56478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4628,41 +4625,60 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Renfansberget (Renfansberget), Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628497</v>
+        <v>628448</v>
       </c>
       <c r="R36" t="n">
-        <v>6645645</v>
+        <v>6645656</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4691,7 +4707,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4701,7 +4717,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4716,22 +4732,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115495166</v>
+        <v>115491753</v>
       </c>
       <c r="B37" t="n">
-        <v>56478</v>
+        <v>96610</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4744,56 +4760,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Renfansberget (Renfansberget), Upl</t>
+          <t>Ekdalsröret (Ekdalsröret), Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628448</v>
+        <v>628163</v>
       </c>
       <c r="R37" t="n">
-        <v>6645656</v>
+        <v>6645680</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4822,7 +4819,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4832,7 +4829,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4859,10 +4856,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115491753</v>
+        <v>115494423</v>
       </c>
       <c r="B38" t="n">
-        <v>96610</v>
+        <v>97650</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4871,25 +4868,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4899,13 +4896,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>628163</v>
+        <v>628205</v>
       </c>
       <c r="R38" t="n">
-        <v>6645680</v>
+        <v>6645809</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4934,7 +4931,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4944,7 +4941,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4959,22 +4956,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115494423</v>
+        <v>115490949</v>
       </c>
       <c r="B39" t="n">
-        <v>97650</v>
+        <v>79558</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4983,38 +4980,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ekdalsröret (Ekdalsröret), Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628205</v>
+        <v>628165</v>
       </c>
       <c r="R39" t="n">
-        <v>6645809</v>
+        <v>6645681</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5046,7 +5052,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5056,7 +5062,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På ek</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5071,22 +5082,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115490949</v>
+        <v>115495325</v>
       </c>
       <c r="B40" t="n">
-        <v>79558</v>
+        <v>90352</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5099,43 +5110,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Renfansberget (Renfansberget), Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628165</v>
+        <v>628501</v>
       </c>
       <c r="R40" t="n">
-        <v>6645681</v>
+        <v>6645648</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5167,7 +5169,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5177,12 +5179,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På ek</t>
+          <t>På mycket gammal tall med hål av spillkråka</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5209,10 +5211,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115495325</v>
+        <v>115490448</v>
       </c>
       <c r="B41" t="n">
-        <v>90352</v>
+        <v>104737</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5221,38 +5223,52 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Renfansberget (Renfansberget), Upl</t>
+          <t>Ekdalsröret (Ekdalsröret), Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628501</v>
+        <v>628146</v>
       </c>
       <c r="R41" t="n">
-        <v>6645648</v>
+        <v>6645564</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5284,7 +5300,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5294,12 +5310,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På mycket gammal tall med hål av spillkråka</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5326,10 +5337,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>115490448</v>
+        <v>115493928</v>
       </c>
       <c r="B42" t="n">
-        <v>104737</v>
+        <v>57281</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5338,40 +5349,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5380,10 +5382,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628146</v>
+        <v>628209</v>
       </c>
       <c r="R42" t="n">
-        <v>6645564</v>
+        <v>6645780</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5415,7 +5417,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5425,7 +5427,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Basen på en död tall full med flisor efter att spillkråka letat hästmyror</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5452,10 +5459,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>115493928</v>
+        <v>116373175</v>
       </c>
       <c r="B43" t="n">
-        <v>57281</v>
+        <v>56490</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5464,31 +5471,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5497,10 +5514,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628209</v>
+        <v>628197</v>
       </c>
       <c r="R43" t="n">
-        <v>6645780</v>
+        <v>6645561</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5527,27 +5544,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Basen på en död tall full med flisor efter att spillkråka letat hästmyror</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5574,65 +5586,64 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>116373175</v>
+        <v>116372637</v>
       </c>
       <c r="B44" t="n">
-        <v>56490</v>
+        <v>57357</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628197</v>
+        <v>628122</v>
       </c>
       <c r="R44" t="n">
-        <v>6645561</v>
+        <v>6645504</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5664,7 +5675,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5674,7 +5685,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ett fåtal trumningar efter uppspelning. Ubgefärlig position, inom 100 m från punkten.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5701,10 +5717,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>116372637</v>
+        <v>116372591</v>
       </c>
       <c r="B45" t="n">
-        <v>57357</v>
+        <v>57634</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5717,36 +5733,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5755,10 +5766,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628122</v>
+        <v>628214</v>
       </c>
       <c r="R45" t="n">
-        <v>6645504</v>
+        <v>6645627</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5790,7 +5801,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5800,12 +5811,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ett fåtal trumningar efter uppspelning. Ubgefärlig position, inom 100 m från punkten.</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5832,14 +5838,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>116372591</v>
+        <v>116373383</v>
       </c>
       <c r="B46" t="n">
-        <v>57634</v>
+        <v>90433</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5848,43 +5854,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ekdalsröret, Ekdalsröret, Upl</t>
+          <t>Ekdalsröret (Ekdalsröret), Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628214</v>
+        <v>628137</v>
       </c>
       <c r="R46" t="n">
-        <v>6645627</v>
+        <v>6645567</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5916,7 +5913,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5926,7 +5923,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5953,10 +5950,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>116373383</v>
+        <v>116373775</v>
       </c>
       <c r="B47" t="n">
-        <v>90433</v>
+        <v>96715</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5965,25 +5962,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5993,10 +5990,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628137</v>
+        <v>628125</v>
       </c>
       <c r="R47" t="n">
-        <v>6645567</v>
+        <v>6645486</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6028,7 +6025,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6038,7 +6035,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6065,10 +6062,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>116373775</v>
+        <v>116373221</v>
       </c>
       <c r="B48" t="n">
-        <v>96715</v>
+        <v>56490</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6081,34 +6078,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ekdalsröret (Ekdalsröret), Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628125</v>
+        <v>628199</v>
       </c>
       <c r="R48" t="n">
-        <v>6645486</v>
+        <v>6645561</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6140,7 +6142,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6150,7 +6152,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6177,10 +6179,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>116373221</v>
+        <v>121063804</v>
       </c>
       <c r="B49" t="n">
-        <v>56490</v>
+        <v>90727</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6189,43 +6191,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628199</v>
+        <v>628125</v>
       </c>
       <c r="R49" t="n">
-        <v>6645561</v>
+        <v>6645764</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6252,22 +6249,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre och någon mindre yngre fruktkropp på vindfälle.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6294,10 +6296,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121063804</v>
+        <v>121063293</v>
       </c>
       <c r="B50" t="n">
-        <v>90727</v>
+        <v>100360</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6306,25 +6308,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6334,10 +6336,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628125</v>
+        <v>628176</v>
       </c>
       <c r="R50" t="n">
-        <v>6645764</v>
+        <v>6645798</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6369,7 +6371,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6379,12 +6381,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre och någon mindre yngre fruktkropp på vindfälle.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6411,10 +6408,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121063293</v>
+        <v>121063691</v>
       </c>
       <c r="B51" t="n">
-        <v>100360</v>
+        <v>98094</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6423,38 +6420,52 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628176</v>
+        <v>628131</v>
       </c>
       <c r="R51" t="n">
-        <v>6645798</v>
+        <v>6645738</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6486,7 +6497,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6496,7 +6507,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6523,10 +6534,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121063691</v>
+        <v>121062863</v>
       </c>
       <c r="B52" t="n">
-        <v>98094</v>
+        <v>105199</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6535,25 +6546,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6563,7 +6574,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6577,10 +6588,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628131</v>
+        <v>628253</v>
       </c>
       <c r="R52" t="n">
-        <v>6645738</v>
+        <v>6645900</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6612,7 +6623,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6622,7 +6633,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>I avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6649,10 +6665,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121062863</v>
+        <v>121075770</v>
       </c>
       <c r="B53" t="n">
-        <v>105199</v>
+        <v>97048</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6665,51 +6681,41 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>628253</v>
+        <v>627994</v>
       </c>
       <c r="R53" t="n">
-        <v>6645900</v>
+        <v>6645755</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6738,7 +6744,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6748,12 +6754,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>I avverkningsanmäld skog</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6762,28 +6763,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121075770</v>
+        <v>121063659</v>
       </c>
       <c r="B54" t="n">
-        <v>97048</v>
+        <v>91324</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6796,41 +6798,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>1339</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ekdalsröret, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>627994</v>
+        <v>628118</v>
       </c>
       <c r="R54" t="n">
-        <v>6645755</v>
+        <v>6645721</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6859,7 +6857,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6869,7 +6867,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6878,29 +6876,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121063659</v>
+        <v>121075787</v>
       </c>
       <c r="B55" t="n">
-        <v>91324</v>
+        <v>79685</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6909,41 +6906,44 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1339</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>628118</v>
+        <v>628029</v>
       </c>
       <c r="R55" t="n">
-        <v>6645721</v>
+        <v>6645577</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6982,7 +6982,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6991,28 +6996,29 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121075787</v>
+        <v>121064006</v>
       </c>
       <c r="B56" t="n">
-        <v>79685</v>
+        <v>97050</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7021,44 +7027,37 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>224363</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ekdalsröret, Upl</t>
+          <t>Uppsala, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628029</v>
+        <v>627998</v>
       </c>
       <c r="R56" t="n">
-        <v>6645577</v>
+        <v>6645748</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7087,7 +7086,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7097,12 +7096,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7111,29 +7105,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121064006</v>
+        <v>121064118</v>
       </c>
       <c r="B57" t="n">
-        <v>97050</v>
+        <v>94616</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7146,19 +7139,23 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>224363</v>
+        <v>2818</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7166,10 +7163,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>627998</v>
+        <v>628010</v>
       </c>
       <c r="R57" t="n">
-        <v>6645748</v>
+        <v>6645722</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7201,7 +7198,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7211,7 +7208,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7238,50 +7235,64 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121064118</v>
+        <v>121063571</v>
       </c>
       <c r="B58" t="n">
-        <v>94616</v>
+        <v>57634</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2818</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Uppsala, Uppsala, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>628010</v>
+        <v>628155</v>
       </c>
       <c r="R58" t="n">
-        <v>6645722</v>
+        <v>6645804</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7313,7 +7324,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7323,7 +7334,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7350,52 +7361,52 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121063571</v>
+        <v>121063186</v>
       </c>
       <c r="B59" t="n">
-        <v>57634</v>
+        <v>98094</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7404,10 +7415,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628155</v>
+        <v>628227</v>
       </c>
       <c r="R59" t="n">
-        <v>6645804</v>
+        <v>6645791</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7439,7 +7450,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7449,7 +7460,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>I avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7473,137 +7489,6 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>121063186</v>
-      </c>
-      <c r="B60" t="n">
-        <v>98094</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>..., ..., Upl</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>628227</v>
-      </c>
-      <c r="R60" t="n">
-        <v>6645791</v>
-      </c>
-      <c r="S60" t="n">
-        <v>4</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Jumkil</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>I avverkningsanmäld skog</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Emil V. Nilsson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Emil V. Nilsson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7490,6 +7490,327 @@
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128690347</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92666</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Rutskinn</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Xylobolus frustulatus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Renfansberget, Renfansberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>628060</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6645591</v>
+      </c>
+      <c r="S60" t="n">
+        <v>4</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128690449</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92666</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Rutskinn</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Xylobolus frustulatus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>628061</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6645579</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Erik Sjödin</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Erik Sjödin</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128690498</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92666</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Rutskinn</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Xylobolus frustulatus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>..., ..., Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>628072</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6645568</v>
+      </c>
+      <c r="S62" t="n">
+        <v>4</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -7495,7 +7495,7 @@
         <v>128690347</v>
       </c>
       <c r="B60" t="n">
-        <v>92666</v>
+        <v>92668</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128690449</v>
       </c>
       <c r="B61" t="n">
-        <v>92666</v>
+        <v>92668</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128690498</v>
       </c>
       <c r="B62" t="n">
-        <v>92666</v>
+        <v>92668</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -7495,7 +7495,7 @@
         <v>128690347</v>
       </c>
       <c r="B60" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128690449</v>
       </c>
       <c r="B61" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128690498</v>
       </c>
       <c r="B62" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -7495,7 +7495,7 @@
         <v>128690347</v>
       </c>
       <c r="B60" t="n">
-        <v>92669</v>
+        <v>92696</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128690449</v>
       </c>
       <c r="B61" t="n">
-        <v>92669</v>
+        <v>92696</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128690498</v>
       </c>
       <c r="B62" t="n">
-        <v>92669</v>
+        <v>92696</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -7495,7 +7495,7 @@
         <v>128690347</v>
       </c>
       <c r="B60" t="n">
-        <v>92696</v>
+        <v>92701</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128690449</v>
       </c>
       <c r="B61" t="n">
-        <v>92696</v>
+        <v>92701</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128690498</v>
       </c>
       <c r="B62" t="n">
-        <v>92696</v>
+        <v>92701</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -7495,7 +7495,7 @@
         <v>128690347</v>
       </c>
       <c r="B60" t="n">
-        <v>92701</v>
+        <v>92706</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128690449</v>
       </c>
       <c r="B61" t="n">
-        <v>92701</v>
+        <v>92706</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128690498</v>
       </c>
       <c r="B62" t="n">
-        <v>92701</v>
+        <v>92706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -7495,7 +7495,7 @@
         <v>128690347</v>
       </c>
       <c r="B60" t="n">
-        <v>92706</v>
+        <v>92710</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128690449</v>
       </c>
       <c r="B61" t="n">
-        <v>92706</v>
+        <v>92710</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128690498</v>
       </c>
       <c r="B62" t="n">
-        <v>92706</v>
+        <v>92710</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -7495,7 +7495,7 @@
         <v>128690347</v>
       </c>
       <c r="B60" t="n">
-        <v>92710</v>
+        <v>92715</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128690449</v>
       </c>
       <c r="B61" t="n">
-        <v>92710</v>
+        <v>92715</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128690498</v>
       </c>
       <c r="B62" t="n">
-        <v>92710</v>
+        <v>92715</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -7495,7 +7495,7 @@
         <v>128690347</v>
       </c>
       <c r="B60" t="n">
-        <v>92718</v>
+        <v>92723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128690449</v>
       </c>
       <c r="B61" t="n">
-        <v>92718</v>
+        <v>92723</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128690498</v>
       </c>
       <c r="B62" t="n">
-        <v>92718</v>
+        <v>92723</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -7495,7 +7495,7 @@
         <v>128690347</v>
       </c>
       <c r="B60" t="n">
-        <v>92723</v>
+        <v>92728</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128690449</v>
       </c>
       <c r="B61" t="n">
-        <v>92723</v>
+        <v>92728</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128690498</v>
       </c>
       <c r="B62" t="n">
-        <v>92723</v>
+        <v>92728</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -7495,7 +7495,7 @@
         <v>128690347</v>
       </c>
       <c r="B60" t="n">
-        <v>92728</v>
+        <v>92731</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128690449</v>
       </c>
       <c r="B61" t="n">
-        <v>92728</v>
+        <v>92731</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128690498</v>
       </c>
       <c r="B62" t="n">
-        <v>92728</v>
+        <v>92731</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -7495,7 +7495,7 @@
         <v>128690347</v>
       </c>
       <c r="B60" t="n">
-        <v>92731</v>
+        <v>92738</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128690449</v>
       </c>
       <c r="B61" t="n">
-        <v>92731</v>
+        <v>92738</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128690498</v>
       </c>
       <c r="B62" t="n">
-        <v>92731</v>
+        <v>92738</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -7816,7 +7816,7 @@
         <v>131239330</v>
       </c>
       <c r="B63" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -7816,7 +7816,7 @@
         <v>131239330</v>
       </c>
       <c r="B63" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 2523-2024 artfynd.xlsx
+++ b/artfynd/A 2523-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63028202</v>
+        <v>81665383</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Falkstensmossen, 600m S om, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628055.7083908524</v>
+        <v>628439</v>
       </c>
       <c r="R2" t="n">
-        <v>6645737.210680514</v>
+        <v>6645631</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,79 +756,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>liten tofs på asp i äldre blandskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63028200</v>
+        <v>81665384</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Falkstensmossen, 500m S om, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628047.130008136</v>
+        <v>628176</v>
       </c>
       <c r="R3" t="n">
-        <v>6645868.854048041</v>
+        <v>6645721</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,79 +853,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>myrholme med barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63028201</v>
+        <v>81665386</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Falkstensmossen, 500m S om, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628053.0513394518</v>
+        <v>628162</v>
       </c>
       <c r="R4" t="n">
-        <v>6645842.972374612</v>
+        <v>6645568</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,74 +950,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>myrholme med barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63028203</v>
+        <v>116373383</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Falkstensmossen, 600m S om, Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628055.7083908524</v>
+        <v>628137</v>
       </c>
       <c r="R5" t="n">
-        <v>6645737.210680514</v>
+        <v>6645567</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,22 +1031,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,85 +1057,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>77201581</v>
+        <v>121063659</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628021.3125240931</v>
+        <v>628118</v>
       </c>
       <c r="R6" t="n">
-        <v>6645801.739781732</v>
+        <v>6645721</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,22 +1138,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-04-22</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-04-22</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81665384</v>
+        <v>104280931</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,37 +1191,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628175.8798447844</v>
+        <v>628048</v>
       </c>
       <c r="R7" t="n">
-        <v>6645720.804544475</v>
+        <v>6645598</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,22 +1246,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-01-06</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-01-06</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt, på grov ek bho 275 cm.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,27 +1281,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>81665386</v>
+        <v>104281064</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,37 +1304,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628162.085117969</v>
+        <v>628059</v>
       </c>
       <c r="R8" t="n">
-        <v>6645567.81053997</v>
+        <v>6645627</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,22 +1359,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-01-06</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-01-06</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ek 274 cm brösthöjdsomkrets.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,27 +1394,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>81665383</v>
+        <v>104287302</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,34 +1417,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Renfansberget, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628438.8071532358</v>
+        <v>628053</v>
       </c>
       <c r="R9" t="n">
-        <v>6645631.092457004</v>
+        <v>6645613</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1570,22 +1471,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-01-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-01-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På ek</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,6 +1490,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1612,15 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104287304</v>
+        <v>104287303</v>
       </c>
       <c r="B10" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628054.8183445517</v>
+        <v>628063</v>
       </c>
       <c r="R10" t="n">
-        <v>6645617.777291794</v>
+        <v>6645640</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1685,19 +1577,9 @@
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="e">
@@ -1727,15 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104287302</v>
+        <v>104287304</v>
       </c>
       <c r="B11" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628052.9667052542</v>
+        <v>628055</v>
       </c>
       <c r="R11" t="n">
-        <v>6645613.197882909</v>
+        <v>6645618</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1800,25 +1677,13 @@
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På ek</t>
-        </is>
+      <c r="AC11" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
@@ -1826,7 +1691,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1845,50 +1709,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104287309</v>
+        <v>104449944</v>
       </c>
       <c r="B12" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renfansberget, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628061.0152138855</v>
+        <v>628043</v>
       </c>
       <c r="R12" t="n">
-        <v>6645612.97485806</v>
+        <v>6645628</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1918,23 +1777,10 @@
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-23</t>
         </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="e">
-        <v>#N/A</v>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
@@ -1948,27 +1794,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Linnéa Sigvardsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Linnéa Sigvardsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104281064</v>
+        <v>104287308</v>
       </c>
       <c r="B13" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,38 +1817,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1467</v>
+        <v>2075</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ekdalsröret, Upl</t>
+          <t>Renfansberget, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628059.0235542697</v>
+        <v>628057</v>
       </c>
       <c r="R13" t="n">
-        <v>6645626.95347597</v>
+        <v>6645597</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2034,25 +1874,13 @@
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ek 274 cm brösthöjdsomkrets.</t>
-        </is>
+      <c r="AC13" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
@@ -2066,27 +1894,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104280931</v>
+        <v>104298425</v>
       </c>
       <c r="B14" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,21 +1917,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1467</v>
+        <v>2075</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2119,13 +1942,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628047.9657549539</v>
+        <v>628054</v>
       </c>
       <c r="R14" t="n">
-        <v>6645597.97370354</v>
+        <v>6645584</v>
       </c>
       <c r="S14" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2149,27 +1972,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt, på grov ek bho 275 cm.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,74 +2002,63 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104281445</v>
+        <v>104444206</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2075</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628039.7644976408</v>
+        <v>628047</v>
       </c>
       <c r="R15" t="n">
-        <v>6645559.058510865</v>
+        <v>6645583</v>
       </c>
       <c r="S15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2278,54 +2085,40 @@
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Zandra Falck</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Zandra Falck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104287308</v>
+        <v>104449946</v>
       </c>
       <c r="B16" t="n">
-        <v>90568</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,14 +2146,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Renfansberget, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628057.0528953329</v>
+        <v>628062</v>
       </c>
       <c r="R16" t="n">
-        <v>6645596.783221409</v>
+        <v>6645601</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2390,23 +2183,10 @@
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-23</t>
         </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="e">
-        <v>#N/A</v>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
@@ -2420,65 +2200,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Linnéa Sigvardsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Linnéa Sigvardsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104287310</v>
+        <v>128690347</v>
       </c>
       <c r="B17" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6428</v>
+        <v>2075</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Renfansberget, Upl</t>
+          <t>Renfansberget, Renfansberget, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628047.1006474758</v>
+        <v>628060</v>
       </c>
       <c r="R17" t="n">
-        <v>6645593.930133006</v>
+        <v>6645591</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2502,26 +2277,23 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="e">
-        <v>#N/A</v>
+          <t>13:25</t>
+        </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
@@ -2547,15 +2319,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104287312</v>
+        <v>128690449</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,37 +2330,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2075</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Renfansberget, Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628046.9271582533</v>
+        <v>628061</v>
       </c>
       <c r="R18" t="n">
-        <v>6645598.941149636</v>
+        <v>6645579</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2617,26 +2384,23 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="e">
-        <v>#N/A</v>
+          <t>13:28</t>
+        </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
@@ -2650,27 +2414,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Erik Sjödin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Erik Sjödin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104287303</v>
+        <v>128690498</v>
       </c>
       <c r="B19" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,37 +2437,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>2075</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Renfansberget, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628062.5879891728</v>
+        <v>628072</v>
       </c>
       <c r="R19" t="n">
-        <v>6645640.121031173</v>
+        <v>6645568</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2732,26 +2491,23 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="e">
-        <v>#N/A</v>
+          <t>13:30</t>
+        </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
@@ -2777,54 +2533,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104298486</v>
+        <v>115492138</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628054.4749450105</v>
+        <v>628157</v>
       </c>
       <c r="R20" t="n">
-        <v>6645584.151382594</v>
+        <v>6645780</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2848,22 +2598,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2878,27 +2628,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104298425</v>
+        <v>115495325</v>
       </c>
       <c r="B21" t="n">
-        <v>90568</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,38 +2651,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2075</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ekdalsröret, Upl</t>
+          <t>Renfansberget, Renfansberget, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628054.4749450105</v>
+        <v>628501</v>
       </c>
       <c r="R21" t="n">
-        <v>6645584.151382594</v>
+        <v>6645648</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2961,22 +2705,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På mycket gammal tall med hål av spillkråka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,27 +2740,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104449944</v>
+        <v>123232282</v>
       </c>
       <c r="B22" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3019,37 +2763,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628042.9092516802</v>
+        <v>628508</v>
       </c>
       <c r="R22" t="n">
-        <v>6645627.90064471</v>
+        <v>6645661</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3073,22 +2817,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3103,68 +2847,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnéa Sigvardsson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnéa Sigvardsson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104434990</v>
+        <v>104287309</v>
       </c>
       <c r="B23" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ekdalsröret, Upl</t>
+          <t>Renfansberget, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628042.5691911092</v>
+        <v>628061</v>
       </c>
       <c r="R23" t="n">
-        <v>6645550.626574364</v>
+        <v>6645613</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3191,20 +2927,13 @@
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
+      <c r="AC23" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
@@ -3212,75 +2941,66 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Zandra Falck</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Zandra Falck</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104444206</v>
+        <v>104287310</v>
       </c>
       <c r="B24" t="n">
-        <v>90568</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2075</v>
+        <v>6428</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ekdalsröret, Upl</t>
+          <t>Renfansberget, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628047.4823243128</v>
+        <v>628047</v>
       </c>
       <c r="R24" t="n">
-        <v>6645582.905872594</v>
+        <v>6645594</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3307,20 +3027,13 @@
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
+      <c r="AC24" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
@@ -3328,56 +3041,50 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Zandra Falck</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Zandra Falck</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104449948</v>
+        <v>104449947</v>
       </c>
       <c r="B25" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3387,10 +3094,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628061.9335836822</v>
+        <v>628062</v>
       </c>
       <c r="R25" t="n">
-        <v>6645600.965832015</v>
+        <v>6645601</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3420,19 +3127,9 @@
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-10-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3459,15 +3156,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104449946</v>
+        <v>115495315</v>
       </c>
       <c r="B26" t="n">
-        <v>90568</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3475,37 +3167,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2075</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628061.9335836822</v>
+        <v>628497</v>
       </c>
       <c r="R26" t="n">
-        <v>6645600.965832015</v>
+        <v>6645645</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3529,22 +3221,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,65 +3251,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnéa Sigvardsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnéa Sigvardsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104449947</v>
+        <v>63028202</v>
       </c>
       <c r="B27" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Falkstensmossen, 600m S om, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628061.9335836822</v>
+        <v>628056</v>
       </c>
       <c r="R27" t="n">
-        <v>6645600.965832015</v>
+        <v>6645737</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3641,22 +3328,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-01-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-01-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3667,69 +3344,79 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>liten tofs på asp i äldre blandskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linnéa Sigvardsson</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linnéa Sigvardsson</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115492128</v>
+        <v>104280753</v>
       </c>
       <c r="B28" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628155</v>
+        <v>628031</v>
       </c>
       <c r="R28" t="n">
-        <v>6645785</v>
+        <v>6645530</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3748,32 +3435,32 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Åland</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På asp, bho 140 cm</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3788,79 +3475,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115493598</v>
+        <v>104287312</v>
       </c>
       <c r="B29" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Renfansberget, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628224</v>
+        <v>628047</v>
       </c>
       <c r="R29" t="n">
-        <v>6645790</v>
+        <v>6645599</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3884,23 +3552,16 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
+          <t>2022-10-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
@@ -3926,53 +3587,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115492138</v>
+        <v>104298486</v>
       </c>
       <c r="B30" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628157</v>
+        <v>628054</v>
       </c>
       <c r="R30" t="n">
-        <v>6645780</v>
+        <v>6645584</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3996,22 +3653,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4026,70 +3683,63 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115495242</v>
+        <v>104434990</v>
       </c>
       <c r="B31" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628490</v>
+        <v>628043</v>
       </c>
       <c r="R31" t="n">
-        <v>6645645</v>
+        <v>6645551</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4113,22 +3763,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4137,33 +3777,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Zandra Falck</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Zandra Falck</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115495579</v>
+        <v>104449948</v>
       </c>
       <c r="B32" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4171,42 +3807,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Renfansberget, Renfansberget, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628430</v>
+        <v>628062</v>
       </c>
       <c r="R32" t="n">
-        <v>6645685</v>
+        <v>6645601</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4230,34 +3861,19 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:39</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Barkflagor borthackade i schackmönster bedömda som trolig tretåig hackspett av Annika Rastén.</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="b">
         <v>0</v>
@@ -4265,62 +3881,66 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Linnéa Sigvardsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Linnéa Sigvardsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115491409</v>
+        <v>115490949</v>
       </c>
       <c r="B33" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628141</v>
+        <v>628165</v>
       </c>
       <c r="R33" t="n">
-        <v>6645698</v>
+        <v>6645681</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4352,7 +3972,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4362,7 +3982,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På ek</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4377,65 +4002,63 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115492559</v>
+        <v>121075787</v>
       </c>
       <c r="B34" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628205</v>
+        <v>628029</v>
       </c>
       <c r="R34" t="n">
-        <v>6645803</v>
+        <v>6645577</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4459,22 +4082,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4483,33 +4111,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115495315</v>
+        <v>131239330</v>
       </c>
       <c r="B35" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4517,37 +4141,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Ekdalsrörstigen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628497</v>
+        <v>628024</v>
       </c>
       <c r="R35" t="n">
-        <v>6645645</v>
+        <v>6645629</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4569,24 +4193,19 @@
           <t>Jumkil</t>
         </is>
       </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>1462</t>
+        </is>
+      </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4597,31 +4216,35 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>2025:1463</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Erik Sjödin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Erik Sjödin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Personlig inventering NES</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115495166</v>
+        <v>77201581</v>
       </c>
       <c r="B36" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4629,21 +4252,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4651,34 +4274,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Renfansberget (Renfansberget), Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628448</v>
+        <v>628021</v>
       </c>
       <c r="R36" t="n">
-        <v>6645656</v>
+        <v>6645802</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4702,22 +4317,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2019-04-22</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2019-04-22</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4744,15 +4359,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115491753</v>
+        <v>115493928</v>
       </c>
       <c r="B37" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4760,37 +4370,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628163</v>
+        <v>628209</v>
       </c>
       <c r="R37" t="n">
-        <v>6645680</v>
+        <v>6645780</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4819,7 +4434,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4829,7 +4444,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Basen på en död tall full med flisor efter att spillkråka letat hästmyror</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4856,50 +4476,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115494423</v>
+        <v>115497368</v>
       </c>
       <c r="B38" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>628205</v>
+        <v>628446</v>
       </c>
       <c r="R38" t="n">
-        <v>6645809</v>
+        <v>6645581</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4931,7 +4551,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4941,7 +4561,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4968,15 +4588,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115490949</v>
+        <v>115495579</v>
       </c>
       <c r="B39" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4984,43 +4599,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Renfansberget, Renfansberget, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628165</v>
+        <v>628430</v>
       </c>
       <c r="R39" t="n">
-        <v>6645681</v>
+        <v>6645685</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5052,7 +4663,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5062,19 +4673,19 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På ek</t>
+          <t>Barkflagor borthackade i schackmönster bedömda som trolig tretåig hackspett av Annika Rastén.</t>
         </is>
       </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG39" t="b">
         <v>0</v>
@@ -5094,15 +4705,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115495325</v>
+        <v>116372637</v>
       </c>
       <c r="B40" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5110,34 +4716,48 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Renfansberget (Renfansberget), Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628501</v>
+        <v>628122</v>
       </c>
       <c r="R40" t="n">
-        <v>6645648</v>
+        <v>6645504</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5164,27 +4784,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På mycket gammal tall med hål av spillkråka</t>
+          <t>Ett fåtal trumningar efter uppspelning. Ubgefärlig position, inom 100 m från punkten.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5211,15 +4831,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115490448</v>
+        <v>77201580</v>
       </c>
       <c r="B41" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5227,51 +4842,48 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628146</v>
+        <v>628021</v>
       </c>
       <c r="R41" t="n">
-        <v>6645564</v>
+        <v>6645802</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5295,22 +4907,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2019-04-22</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2019-04-22</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5337,58 +4949,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>115493928</v>
+        <v>81665389</v>
       </c>
       <c r="B42" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628209</v>
+        <v>628164</v>
       </c>
       <c r="R42" t="n">
-        <v>6645780</v>
+        <v>6645715</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5412,27 +5014,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Basen på en död tall full med flisor efter att spillkråka letat hästmyror</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5459,15 +5046,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>116373175</v>
+        <v>115495166</v>
       </c>
       <c r="B43" t="n">
-        <v>56490</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5492,7 +5074,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>adult</t>
@@ -5505,22 +5091,22 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Renfansberget, Renfansberget, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628197</v>
+        <v>628448</v>
       </c>
       <c r="R43" t="n">
-        <v>6645561</v>
+        <v>6645656</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5544,22 +5130,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5586,52 +5172,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>116372637</v>
+        <v>115495242</v>
       </c>
       <c r="B44" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5640,13 +5212,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628122</v>
+        <v>628490</v>
       </c>
       <c r="R44" t="n">
-        <v>6645504</v>
+        <v>6645645</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5670,27 +5242,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ett fåtal trumningar efter uppspelning. Ubgefärlig position, inom 100 m från punkten.</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5705,71 +5272,67 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>116372591</v>
+        <v>115495983</v>
       </c>
       <c r="B45" t="n">
-        <v>57634</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ekdalsröret, Ekdalsröret, Upl</t>
+          <t>NV Renfansberget, NV Renfansberget, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628214</v>
+        <v>628649</v>
       </c>
       <c r="R45" t="n">
-        <v>6645627</v>
+        <v>6645577</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5796,22 +5359,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Natträd</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5838,50 +5406,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>116373383</v>
+        <v>115496236</v>
       </c>
       <c r="B46" t="n">
-        <v>90433</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628137</v>
+        <v>628446</v>
       </c>
       <c r="R46" t="n">
-        <v>6645567</v>
+        <v>6645581</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5908,22 +5476,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5938,27 +5506,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>116373775</v>
+        <v>115496745</v>
       </c>
       <c r="B47" t="n">
-        <v>96715</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5966,34 +5529,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>NV Renfansberget, NV Renfansberget, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628125</v>
+        <v>628259</v>
       </c>
       <c r="R47" t="n">
-        <v>6645486</v>
+        <v>6645485</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6020,22 +5588,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6062,15 +5630,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>116373221</v>
+        <v>116373175</v>
       </c>
       <c r="B48" t="n">
-        <v>56490</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6096,18 +5659,28 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ekdalsröret (Ekdalsröret), Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628199</v>
+        <v>628197</v>
       </c>
       <c r="R48" t="n">
         <v>6645561</v>
@@ -6142,7 +5715,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6152,7 +5725,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6179,50 +5752,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121063804</v>
+        <v>116373221</v>
       </c>
       <c r="B49" t="n">
-        <v>90727</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628125</v>
+        <v>628199</v>
       </c>
       <c r="R49" t="n">
-        <v>6645764</v>
+        <v>6645561</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6249,27 +5822,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre och någon mindre yngre fruktkropp på vindfälle.</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6296,15 +5864,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121063293</v>
+        <v>63028200</v>
       </c>
       <c r="B50" t="n">
-        <v>100360</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6312,37 +5875,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Falkstensmossen, 500m S om, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628176</v>
+        <v>628047</v>
       </c>
       <c r="R50" t="n">
-        <v>6645798</v>
+        <v>6645869</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6366,22 +5934,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2017-01-26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2017-01-26</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6392,83 +5950,74 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>myrholme med barrskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121063691</v>
+        <v>63028201</v>
       </c>
       <c r="B51" t="n">
-        <v>98094</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Falkstensmossen, 500m S om, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628131</v>
+        <v>628053</v>
       </c>
       <c r="R51" t="n">
-        <v>6645738</v>
+        <v>6645843</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6492,22 +6041,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2017-01-26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2017-01-26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6518,80 +6057,75 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>myrholme med barrskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121062863</v>
+        <v>116372591</v>
       </c>
       <c r="B52" t="n">
-        <v>105199</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628253</v>
+        <v>628214</v>
       </c>
       <c r="R52" t="n">
-        <v>6645900</v>
+        <v>6645627</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6618,27 +6152,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>I avverkningsanmäld skog</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6665,57 +6194,62 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121075770</v>
+        <v>121063571</v>
       </c>
       <c r="B53" t="n">
-        <v>97048</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ekdalsröret, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>627994</v>
+        <v>628155</v>
       </c>
       <c r="R53" t="n">
-        <v>6645755</v>
+        <v>6645804</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6744,7 +6278,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6754,7 +6288,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6763,72 +6297,75 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121063659</v>
+        <v>104281445</v>
       </c>
       <c r="B54" t="n">
-        <v>91324</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>628118</v>
+        <v>628039</v>
       </c>
       <c r="R54" t="n">
-        <v>6645721</v>
+        <v>6645559</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6852,22 +6389,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6882,68 +6419,64 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121075787</v>
+        <v>114700664</v>
       </c>
       <c r="B55" t="n">
-        <v>79685</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>628029</v>
+        <v>628040</v>
       </c>
       <c r="R55" t="n">
-        <v>6645577</v>
+        <v>6645559</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6965,29 +6498,19 @@
           <t>Jumkil</t>
         </is>
       </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C-Upp-0700</t>
+        </is>
+      </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6996,65 +6519,81 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121064006</v>
+        <v>115493598</v>
       </c>
       <c r="B56" t="n">
-        <v>97050</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>224363</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Uppsala, Uppsala, Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>627998</v>
+        <v>628224</v>
       </c>
       <c r="R56" t="n">
-        <v>6645748</v>
+        <v>6645790</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7081,22 +6620,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7123,50 +6662,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121064118</v>
+        <v>115494423</v>
       </c>
       <c r="B57" t="n">
-        <v>94616</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Uppsala, Uppsala, Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628010</v>
+        <v>628205</v>
       </c>
       <c r="R57" t="n">
-        <v>6645722</v>
+        <v>6645809</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7193,22 +6727,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7223,64 +6757,59 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121063571</v>
+        <v>121063186</v>
       </c>
       <c r="B58" t="n">
-        <v>57634</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7289,10 +6818,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>628155</v>
+        <v>628227</v>
       </c>
       <c r="R58" t="n">
-        <v>6645804</v>
+        <v>6645791</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7324,7 +6853,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7334,7 +6863,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>I avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7361,15 +6895,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121063186</v>
+        <v>121063691</v>
       </c>
       <c r="B59" t="n">
-        <v>98094</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7396,7 +6925,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7406,7 +6935,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7415,10 +6944,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628227</v>
+        <v>628131</v>
       </c>
       <c r="R59" t="n">
-        <v>6645791</v>
+        <v>6645738</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7450,7 +6979,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7460,12 +6989,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>I avverkningsanmäld skog</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7492,45 +7016,59 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128690347</v>
+        <v>115490448</v>
       </c>
       <c r="B60" t="n">
-        <v>92738</v>
+        <v>106244</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2075</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Renfansberget, Renfansberget, Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628060</v>
+        <v>628146</v>
       </c>
       <c r="R60" t="n">
-        <v>6645591</v>
+        <v>6645564</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7557,22 +7095,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7599,32 +7137,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128690449</v>
+        <v>115491409</v>
       </c>
       <c r="B61" t="n">
-        <v>92738</v>
+        <v>106244</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2075</v>
+        <v>221144</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7634,13 +7172,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>628061</v>
+        <v>628141</v>
       </c>
       <c r="R61" t="n">
-        <v>6645579</v>
+        <v>6645698</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7664,22 +7202,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7694,60 +7232,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erik Sjödin</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erik Sjödin</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128690498</v>
+        <v>115497113</v>
       </c>
       <c r="B62" t="n">
-        <v>92738</v>
+        <v>106244</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2075</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>..., ..., Upl</t>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>628072</v>
+        <v>628446</v>
       </c>
       <c r="R62" t="n">
-        <v>6645568</v>
+        <v>6645581</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7771,22 +7309,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7801,60 +7339,74 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131239330</v>
+        <v>121062863</v>
       </c>
       <c r="B63" t="n">
-        <v>80369</v>
+        <v>106244</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ekdalsrörstigen, Upl</t>
+          <t>..., ..., Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>628024</v>
+        <v>628253</v>
       </c>
       <c r="R63" t="n">
-        <v>6645629</v>
+        <v>6645900</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7876,19 +7428,29 @@
           <t>Jumkil</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>1462</t>
-        </is>
-      </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>I avverkningsanmäld skog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7899,28 +7461,979 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>2025:1463</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erik Sjödin</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erik Sjödin</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Personlig inventering NES</t>
-        </is>
-      </c>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63028203</v>
+      </c>
+      <c r="B64" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Falkstensmossen, 600m S om, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>628056</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6645737</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>115491753</v>
+      </c>
+      <c r="B65" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>628163</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6645680</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>115492128</v>
+      </c>
+      <c r="B66" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>628155</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6645785</v>
+      </c>
+      <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>115492559</v>
+      </c>
+      <c r="B67" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>628205</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6645803</v>
+      </c>
+      <c r="S67" t="n">
+        <v>4</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>116373775</v>
+      </c>
+      <c r="B68" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>628125</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6645486</v>
+      </c>
+      <c r="S68" t="n">
+        <v>4</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>121075770</v>
+      </c>
+      <c r="B69" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Ekdalsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>627994</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6645755</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Eric Grund</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Eric Grund</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>121063293</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>..., ..., Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>628176</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6645798</v>
+      </c>
+      <c r="S70" t="n">
+        <v>4</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>115496919</v>
+      </c>
+      <c r="B71" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Ekdalsröret, Ekdalsröret, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>628446</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6645581</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>121064006</v>
+      </c>
+      <c r="B72" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Uppsala, Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>627998</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6645748</v>
+      </c>
+      <c r="S72" t="n">
+        <v>4</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
